--- a/experiments/results/densenet101/CIFAR-100/ReAct+DICE/adaptive/avg/results.xlsx
+++ b/experiments/results/densenet101/CIFAR-100/ReAct+DICE/adaptive/avg/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -1399,6 +1399,153 @@
         <v>91.73</v>
       </c>
       <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=90,ash_p=None,react_th=1.6,scale_th=0.01,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>93.92</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>92.20999999999999</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>91.38</v>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.5,scale_th=0.01,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>96.87</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>87.76000000000001</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>33.13</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>94.38</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>31.44</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>99.51000000000001</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>94.12</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>34.39</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=90,ash_p=None,react_th=1.5,scale_th=0.01,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>96.93000000000001</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>86.87</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>72.81999999999999</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>94.55</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>99.56</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>94.34</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>dice_p=90,ash_p=None,react_th=1.6,scale_th=0.01,type=avg</t>
         </is>
